--- a/docs/data/beidan_26079_dashboard.xlsx
+++ b/docs/data/beidan_26079_dashboard.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,12 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <i val="1"/>
+      <color rgb="00888888"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="微软雅黑"/>
@@ -117,31 +123,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -520,3159 +527,3166 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26079期 比赛看板 — 2026-07-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>⚽ 北京单场26079期 比赛看板（皇冠历史相同亚盘） — 2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>数据来源：500.com 皇冠公司（cid=280）历史相同亚盘概率</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>联赛</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>开赛时间</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>主队</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>让球(胜平负)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>客队</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>亚盘(胜负过关)</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>历史概率% (主胜)</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>历史概率% (平)</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>历史概率% (客胜)</t>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>皇冠历史概率% (主胜)</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>皇冠历史概率% (平)</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>皇冠历史概率% (客胜)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>欧冠资格</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>07-29 00:00</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>林肯红魔</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>米亚尔比</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>受一球/球半</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>瑞典甲</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>07-29 01:00</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>兰斯科罗纳</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>北雪平</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>瑞典甲</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>07-29 01:00</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>赫尔辛堡</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>北欧联FC</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>欧冠资格</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>07-29 02:45</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>哈茨</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>格拉茨风暴</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>南俱杯</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>07-29 06:00</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>堤格雷</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>乌拉圭民族</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>阿职联</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>07-29 06:00</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>圣洛伦索</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>门多萨体操击剑</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>阿职联</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>07-29 06:00</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>班菲尔德</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>萨米恩托</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>巴西乙</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>07-29 06:30</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>庞特普雷塔</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>巴西竞技</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>巴西乙</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>07-29 06:30</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>尤文图德</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>阿瓦伊</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>一球</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>阿职联</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>07-29 08:15</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>阿根廷青年人</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>里奥夸尔托学生队</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>阿职联</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>07-29 08:15</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>罗萨里奥中央</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>竞技</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>南俱杯</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>07-29 08:30</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>桑托斯</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>委内瑞拉中央大学</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>球半/两球</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>巴西乙</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>07-29 08:35</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>福塔雷萨</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>博塔弗戈SP</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>韩足总杯</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>07-29 18:00</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>光州FC</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>天安城</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>韩足总杯</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>07-29 18:00</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>仁川联</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>金浦市民</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>韩足总杯</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>07-29 18:00</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>金泉尚武</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>水原FC</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>韩足总杯</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>07-29 18:00</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>釜山偶像</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>FC首尔</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>韩足总杯</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>07-29 18:00</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>富川FC</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>坡州前线</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J21" s="6" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>韩足总杯</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>07-29 18:30</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>忠北清州</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>安养FC</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>韩足总杯</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>07-29 18:30</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>济州SK FC</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>华城FC</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J23" s="6" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>韩足总杯</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>07-29 19:00</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>金海</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>城南FC</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>欧冠资格</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>07-29 23:00</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>凯拉特</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>奥莫尼亚</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>芬甲</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>07-29 23:30</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>MP米克力</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>卡亚尼卡帕</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>欧冠资格</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>07-30 01:00</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>波兹南莱赫</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>奥胡斯</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
       </c>
-      <c r="J27" s="6" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>阿职联</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>07-30 01:30</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>巴拉卡斯中央</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>阿尔多斯维</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>欧冠资格</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>07-30 02:00</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>贝尔格莱德红星</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>拉恩</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>两球半/三球</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J29" s="6" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>欧冠资格</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>07-30 02:00</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>扎布热矿工</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>费内巴切</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>受一球</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>阿职联</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>07-30 04:00</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>国防与司法</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>利斯特雷</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>南俱杯</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>07-30 06:00</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>瓦斯科达伽马</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>麦德林独立</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>阿职联</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>07-30 06:15</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>拉普拉塔体操</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>河床</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J33" s="6" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>巴西甲</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>07-30 06:30</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>巴西国际</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>弗拉门戈</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>巴西甲</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>07-30 06:30</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>米拉索</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>雷莫</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="J35" s="6" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>南俱杯</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>07-30 08:30</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>布拉干蒂诺RB</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>水晶竞技</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>球半</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>南俱杯</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>07-30 08:30</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>西恩夏诺</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>拉努斯</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>54%</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>巴西甲</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>07-30 08:30</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>弗鲁米嫩塞</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>巴伊亚</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>巴西甲</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>07-30 08:30</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>维多利亚</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>帕尔梅拉斯</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J39" s="6" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>阿职联</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>07-30 08:30</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>科尔多瓦学院</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>普拉滕斯</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>芬甲</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>07-30 23:30</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>基柏</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>查普斯</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>一球</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
       </c>
-      <c r="J41" s="6" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>欧协资格</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>07-31 00:00</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>图尔库国际</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>巴萨克赛尔</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>受半球/一球</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr">
+      <c r="I42" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>欧协资格</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>07-31 00:00</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>埃尔维斯</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>斯塔尔南</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I43" s="4" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>欧罗巴资格</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>07-31 01:00</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>赫拉德茨</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>特罗姆瑟</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
+      <c r="I44" s="4" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
+      <c r="A45" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>欧罗巴资格</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>07-31 01:00</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>中日德兰</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>贝西克塔斯</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
       </c>
-      <c r="I45" s="4" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J45" s="4" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>欧协资格</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>07-31 01:00</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>佩特罗古</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>巴尼亚卢卡战士</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
+      <c r="I46" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="J46" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
+      <c r="A47" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>欧协资格</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>07-31 01:00</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>北西兰</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E47" s="8" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>哥德堡盖斯</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>一球</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="I47" s="4" t="inlineStr">
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>欧协资格</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>07-31 01:00</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>布兰</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>克卢日大学</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="J48" s="3" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>欧协资格</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>07-31 01:30</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>新圣徒</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>塔林弗洛拉</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>欧协资格</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>07-31 01:30</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>德里城</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>里耶卡</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>受半球/一球</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>欧罗巴资格</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>07-31 02:00</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>索非亚中央陆军</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>卡拉巴克</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>平手</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="I51" s="4" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
       </c>
-      <c r="J51" s="6" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>欧协资格</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>07-31 02:00</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>维斯特里</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>里加足球学院</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>受球半/两球</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr">
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="J52" s="4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n">
+      <c r="A53" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>欧罗巴资格</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>07-31 02:30</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>安德莱赫特</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>哈马比</t>
         </is>
       </c>
-      <c r="G53" s="4" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="I53" s="4" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J53" s="4" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>欧罗巴资格</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>07-31 02:30</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>费伦茨瓦罗斯</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>特温特</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H54" s="4" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr">
+      <c r="I54" s="4" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
+      <c r="J54" s="4" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n">
+      <c r="A55" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>欧协资格</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>07-31 02:30</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>日林斯基</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E55" s="8" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>瓦鲁尔</t>
         </is>
       </c>
-      <c r="G55" s="4" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>球半</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I55" s="4" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="J55" s="6" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>欧罗巴资格</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>07-31 03:00</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>本菲卡</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>圣加仑</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="G56" s="4" t="inlineStr">
         <is>
           <t>两球</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="H56" s="4" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr">
+      <c r="I56" s="4" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="J56" s="3" t="inlineStr">
+      <c r="J56" s="4" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n">
+      <c r="A57" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>南俱杯</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>07-31 06:00</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>格雷米奥</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E57" s="8" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>玻利瓦尔</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr">
+      <c r="H57" s="5" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="I57" s="4" t="inlineStr">
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
       </c>
-      <c r="J57" s="5" t="inlineStr">
+      <c r="J57" s="6" t="inlineStr">
         <is>
           <t>54%</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>阿职联</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>07-31 06:00</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>塔勒瑞斯</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>萨斯菲尔德</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="G58" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="H58" s="4" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="I58" s="3" t="inlineStr">
+      <c r="I58" s="4" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="J58" s="3" t="inlineStr">
+      <c r="J58" s="4" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
+      <c r="A59" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>阿职联</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>07-31 06:00</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>门多萨独立</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>飓风队</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
         </is>
       </c>
-      <c r="H59" s="6" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="I59" s="6" t="inlineStr">
+      <c r="I59" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="J59" s="4" t="inlineStr">
+      <c r="J59" s="5" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>巴西甲</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>07-31 06:30</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>科林蒂安</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>巴拉纳竞技</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>半球</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr">
+      <c r="I60" s="4" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="J60" s="3" t="inlineStr">
+      <c r="J60" s="4" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
+      <c r="A61" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>阿职联</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>07-31 08:15</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>科尔多瓦中央</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>图库曼竞技</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H61" s="6" t="inlineStr">
+      <c r="H61" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr">
+      <c r="I61" s="5" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="J61" s="6" t="inlineStr">
+      <c r="J61" s="7" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>阿职联</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>07-31 08:15</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>阿根廷独立</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>纽维尔老男孩</t>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="H62" s="4" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="I62" s="3" t="inlineStr">
+      <c r="I62" s="4" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="J62" s="3" t="inlineStr">
+      <c r="J62" s="4" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n">
+      <c r="A63" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>南俱杯</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>07-31 08:30</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>奥伊金斯</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="F63" s="5" t="inlineStr">
         <is>
           <t>博卡青年</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr">
+      <c r="H63" s="5" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I63" s="6" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
       </c>
-      <c r="J63" s="4" t="inlineStr">
+      <c r="J63" s="5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>南俱杯</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>07-31 08:30</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>加拉加斯</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>圣塔菲</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr">
+      <c r="I64" s="4" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
       </c>
-      <c r="J64" s="3" t="inlineStr">
+      <c r="J64" s="4" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" s="9" t="inlineStr">
         <is>
           <t>共 61 场比赛</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="inlineStr">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>图例：</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="10" t="inlineStr">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>让球为负（主队让球）</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="12" t="inlineStr">
+      <c r="A70" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>让球为正（客队让球）</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="13" t="inlineStr">
+      <c r="A71" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>历史概率≥45%</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="14" t="inlineStr">
+      <c r="A72" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>历史概率≥35%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/beidan_26079_dashboard.xlsx
+++ b/docs/data/beidan_26079_dashboard.xlsx
@@ -1277,20 +1277,24 @@
           <t>天安城</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>45%</t>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>半球/一球</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1465,20 +1469,24 @@
           <t>坡州前线</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>一球</t>
+        </is>
+      </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>70%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>

--- a/docs/data/beidan_26079_dashboard.xlsx
+++ b/docs/data/beidan_26079_dashboard.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26079期 比赛看板（皇冠历史相同亚盘） — 2026-07-28</t>
+          <t>⚽ 北京单场26079期 比赛看板（皇冠历史相同亚盘） — 2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1327,20 +1327,24 @@
           <t>金浦市民</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>受一球</t>
+        </is>
+      </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1423,20 +1427,24 @@
           <t>FC首尔</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>受半球/一球</t>
+        </is>
+      </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1519,20 +1527,24 @@
           <t>安养FC</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>受平手/半球</t>
+        </is>
+      </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1565,20 +1577,24 @@
           <t>华城FC</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>半球/一球</t>
+        </is>
+      </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>70%</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1611,20 +1627,24 @@
           <t>城南FC</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>受平手/半球</t>
+        </is>
+      </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>

--- a/docs/data/beidan_26079_dashboard.xlsx
+++ b/docs/data/beidan_26079_dashboard.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26079期 比赛看板（皇冠历史相同亚盘） — 2026-07-29</t>
+          <t>⚽ 北京单场26079期 比赛看板（皇冠历史相同亚盘） — 2026-07-30</t>
         </is>
       </c>
     </row>
